--- a/prospetto_libri.xlsx
+++ b/prospetto_libri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2470A836-CF96-1A4D-8755-C88FCEBB74D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700CBEC3-C018-B14B-A3ED-F39428DF6293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{88358FA3-2BA6-2D4E-B9E0-7663A633FBB9}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{88358FA3-2BA6-2D4E-B9E0-7663A633FBB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -62,60 +62,30 @@
     <t>Deserto</t>
   </si>
   <si>
-    <t>1513 a.C.</t>
-  </si>
-  <si>
-    <t>"In principio" a 1657 a.C.</t>
-  </si>
-  <si>
     <t>Esodo</t>
   </si>
   <si>
-    <t>1512 a.C.</t>
-  </si>
-  <si>
-    <t>1657–1512 a.C.</t>
-  </si>
-  <si>
     <t>Levitico</t>
   </si>
   <si>
-    <t>1 mese (1512 a.C.)</t>
-  </si>
-  <si>
     <t>Numeri</t>
   </si>
   <si>
     <t>Deserto e pianure di Moab</t>
   </si>
   <si>
-    <t>1473 a.C.</t>
-  </si>
-  <si>
-    <t>1512–1473 a.C.</t>
-  </si>
-  <si>
     <t>Deuteronomio</t>
   </si>
   <si>
     <t>Pianure di Moab</t>
   </si>
   <si>
-    <t>2 mesi (1473 a.C.)</t>
-  </si>
-  <si>
     <t>Giosuè</t>
   </si>
   <si>
     <t>Canaan</t>
   </si>
   <si>
-    <t>c. 1450 a.C.</t>
-  </si>
-  <si>
-    <t>1473–c. 1450 a.C.</t>
-  </si>
-  <si>
     <t>Giudici</t>
   </si>
   <si>
@@ -125,18 +95,9 @@
     <t>Israele</t>
   </si>
   <si>
-    <t>c. 1100 a.C.</t>
-  </si>
-  <si>
-    <t>c. 1450–c. 1120 a.C.</t>
-  </si>
-  <si>
     <t>Rut</t>
   </si>
   <si>
-    <t>c. 1090 a.C.</t>
-  </si>
-  <si>
     <t>11 anni dei Giudici</t>
   </si>
   <si>
@@ -146,24 +107,12 @@
     <t>Samuele; Gad; Natan</t>
   </si>
   <si>
-    <t>c. 1078 a.C.</t>
-  </si>
-  <si>
-    <t>c. 1180–1078 a.C.</t>
-  </si>
-  <si>
     <t>2 Samuele</t>
   </si>
   <si>
     <t>Gad; Natan</t>
   </si>
   <si>
-    <t>c. 1040 a.C.</t>
-  </si>
-  <si>
-    <t>1077–c. 1040 a.C.</t>
-  </si>
-  <si>
     <t>1 Re</t>
   </si>
   <si>
@@ -173,21 +122,12 @@
     <t>Gerusalemme e Giuda</t>
   </si>
   <si>
-    <t>580 a.C.</t>
-  </si>
-  <si>
-    <t>c. 1027–910 a.C.</t>
-  </si>
-  <si>
     <t>2 Re</t>
   </si>
   <si>
     <t>Egitto</t>
   </si>
   <si>
-    <t>c. 920–580 a.C.</t>
-  </si>
-  <si>
     <t>1 Cronache</t>
   </si>
   <si>
@@ -197,33 +137,15 @@
     <t>Gerusalemme (?)</t>
   </si>
   <si>
-    <t>c. 460 a.C.</t>
-  </si>
-  <si>
-    <t>Dopo 1 Cronache 9:44: 1077–1037 a.C.</t>
-  </si>
-  <si>
     <t>2 Cronache</t>
   </si>
   <si>
-    <t>1037–537 a.C.</t>
-  </si>
-  <si>
     <t>Gerusalemme</t>
   </si>
   <si>
-    <t>537–c. 467 a.C.</t>
-  </si>
-  <si>
     <t>Neemia</t>
   </si>
   <si>
-    <t>dopo il 443 a.C.</t>
-  </si>
-  <si>
-    <t>456–dopo il 443 a.C.</t>
-  </si>
-  <si>
     <t>Ester</t>
   </si>
   <si>
@@ -233,21 +155,9 @@
     <t>Susa, Elam</t>
   </si>
   <si>
-    <t>c. 475 a.C.</t>
-  </si>
-  <si>
-    <t>493–c. 475 a.C.</t>
-  </si>
-  <si>
     <t>Giobbe</t>
   </si>
   <si>
-    <t>c. 1473 a.C.</t>
-  </si>
-  <si>
-    <t>Oltre 140 anni tra il 1657 e il 1473 a.C.</t>
-  </si>
-  <si>
     <t>Salmi</t>
   </si>
   <si>
@@ -263,156 +173,78 @@
     <t>Salomone; Agur; Lemuel</t>
   </si>
   <si>
-    <t>c. 717 a.C.</t>
-  </si>
-  <si>
     <t>Ecclesiaste / Ecclesiaste</t>
   </si>
   <si>
     <t>Salomone</t>
   </si>
   <si>
-    <t>prima del 1000 a.C.</t>
-  </si>
-  <si>
     <t>Il Cantico dei Cantici</t>
   </si>
   <si>
-    <t>c. 1020 a.C.</t>
-  </si>
-  <si>
     <t>Isaia</t>
   </si>
   <si>
-    <t>dopo il 732 a.C.</t>
-  </si>
-  <si>
-    <t>c. 778–dopo il 732 a.C.</t>
-  </si>
-  <si>
     <t>Giuda ed Egitto</t>
   </si>
   <si>
-    <t>647–580 a.C.</t>
-  </si>
-  <si>
     <t>Lamentazioni</t>
   </si>
   <si>
     <t>Presso Gerusalemme</t>
   </si>
   <si>
-    <t>607 a.C.</t>
-  </si>
-  <si>
     <t>Ezechiele</t>
   </si>
   <si>
     <t>Babilonia</t>
   </si>
   <si>
-    <t>c. 591 a.C.</t>
-  </si>
-  <si>
-    <t>613–c. 591 a.C.</t>
-  </si>
-  <si>
     <t>Daniele</t>
   </si>
   <si>
-    <t>c. 536 a.C.</t>
-  </si>
-  <si>
-    <t>618–c. 536 a.C.</t>
-  </si>
-  <si>
     <t>Osea</t>
   </si>
   <si>
     <t>Samaria (Distretto)</t>
   </si>
   <si>
-    <t>dopo il 745 a.C.</t>
-  </si>
-  <si>
-    <t>prima del 804–dopo il 745 a.C.</t>
-  </si>
-  <si>
     <t>Gioele</t>
   </si>
   <si>
     <t>Giuda</t>
   </si>
   <si>
-    <t>c. 820 a.C. (?)</t>
-  </si>
-  <si>
     <t>Amos</t>
   </si>
   <si>
-    <t>c. 804 a.C.</t>
-  </si>
-  <si>
     <t>Abdia</t>
   </si>
   <si>
-    <t>c. 607 a.C.</t>
-  </si>
-  <si>
     <t>Giona</t>
   </si>
   <si>
-    <t>c. 844 a.C.</t>
-  </si>
-  <si>
     <t>Michea</t>
   </si>
   <si>
-    <t>prima del 717 a.C.</t>
-  </si>
-  <si>
-    <t>c. 777–717 a.C.</t>
-  </si>
-  <si>
     <t>Naum</t>
   </si>
   <si>
-    <t>prima del 632 a.C.</t>
-  </si>
-  <si>
     <t>Abacuc</t>
   </si>
   <si>
-    <t>c. 628 a.C. (?)</t>
-  </si>
-  <si>
     <t>Sofonia</t>
   </si>
   <si>
-    <t>prima del 648 a.C.</t>
-  </si>
-  <si>
     <t>Aggeo</t>
   </si>
   <si>
     <t>Gerusalemme ricostruita</t>
   </si>
   <si>
-    <t>520 a.C.</t>
-  </si>
-  <si>
-    <t>112 giorni (520 a.C.)</t>
-  </si>
-  <si>
     <t>Zaccaria</t>
   </si>
   <si>
-    <t>518 a.C.</t>
-  </si>
-  <si>
-    <t>520–518 a.C.</t>
-  </si>
-  <si>
     <t>Malachia</t>
   </si>
   <si>
@@ -422,36 +254,18 @@
     <t>Palestina</t>
   </si>
   <si>
-    <t>c. 41 d.C.</t>
-  </si>
-  <si>
-    <t>2 a.C.–33 d.C.</t>
-  </si>
-  <si>
     <t>Marco</t>
   </si>
   <si>
     <t>Roma</t>
   </si>
   <si>
-    <t>c. 60–65 d.C.</t>
-  </si>
-  <si>
-    <t>29–33 d.C.</t>
-  </si>
-  <si>
     <t>Luca</t>
   </si>
   <si>
     <t>Cesarea</t>
   </si>
   <si>
-    <t>c. 56–58 d.C.</t>
-  </si>
-  <si>
-    <t>3 a.C.–33 d.C.</t>
-  </si>
-  <si>
     <t>Giovanni</t>
   </si>
   <si>
@@ -461,21 +275,9 @@
     <t>Efeso o vicinanze</t>
   </si>
   <si>
-    <t>c. 98 d.C.</t>
-  </si>
-  <si>
-    <t>Dopo il prologo, 29–33 d.C.</t>
-  </si>
-  <si>
     <t>Atti</t>
   </si>
   <si>
-    <t>c. 61 d.C.</t>
-  </si>
-  <si>
-    <t>33–c. 61 d.C.</t>
-  </si>
-  <si>
     <t>Romani</t>
   </si>
   <si>
@@ -485,18 +287,12 @@
     <t>Corinto</t>
   </si>
   <si>
-    <t>c. 56 d.C.</t>
-  </si>
-  <si>
     <t>1 Corinti</t>
   </si>
   <si>
     <t>Efeso</t>
   </si>
   <si>
-    <t>c. 55 d.C.</t>
-  </si>
-  <si>
     <t>2 Corinti</t>
   </si>
   <si>
@@ -509,15 +305,9 @@
     <t>Corinto o Antiochia di Siria</t>
   </si>
   <si>
-    <t>c. 50–52 d.C.</t>
-  </si>
-  <si>
     <t>Efesini</t>
   </si>
   <si>
-    <t>c. 60–61 d.C.</t>
-  </si>
-  <si>
     <t>Filippesi</t>
   </si>
   <si>
@@ -527,27 +317,15 @@
     <t>1 Tessalonicesi</t>
   </si>
   <si>
-    <t>c. 50 d.C.</t>
-  </si>
-  <si>
     <t>2 Tessalonicesi</t>
   </si>
   <si>
-    <t>c. 51 d.C.</t>
-  </si>
-  <si>
     <t>1 Timoteo</t>
   </si>
   <si>
-    <t>c. 61–64 d.C.</t>
-  </si>
-  <si>
     <t>2 Timoteo</t>
   </si>
   <si>
-    <t>c. 65 d.C.</t>
-  </si>
-  <si>
     <t>Tito</t>
   </si>
   <si>
@@ -566,27 +344,18 @@
     <t>Giacomo (fratello di Gesù)</t>
   </si>
   <si>
-    <t>prima del 62 d.C.</t>
-  </si>
-  <si>
     <t>1 Pietro</t>
   </si>
   <si>
     <t>Pietro</t>
   </si>
   <si>
-    <t>c. 62–64 d.C.</t>
-  </si>
-  <si>
     <t>2 Pietro</t>
   </si>
   <si>
     <t>Babilonia (?)</t>
   </si>
   <si>
-    <t>c. 64 d.C.</t>
-  </si>
-  <si>
     <t>1 Giovanni</t>
   </si>
   <si>
@@ -608,7 +377,238 @@
     <t>Patmos</t>
   </si>
   <si>
-    <t>c. 96 d.C.</t>
+    <t>1513 a.E.V.</t>
+  </si>
+  <si>
+    <t>"In principio" a 1657 a.E.V.</t>
+  </si>
+  <si>
+    <t>1512 a.E.V.</t>
+  </si>
+  <si>
+    <t>1657–1512 a.E.V.</t>
+  </si>
+  <si>
+    <t>1 mese (1512 a.E.V.)</t>
+  </si>
+  <si>
+    <t>1473 a.E.V.</t>
+  </si>
+  <si>
+    <t>1512–1473 a.E.V.</t>
+  </si>
+  <si>
+    <t>2 mesi (1473 a.E.V.)</t>
+  </si>
+  <si>
+    <t>c. 1450 a.E.V.</t>
+  </si>
+  <si>
+    <t>1473–c. 1450 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1100 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1450–c. 1120 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1090 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1078 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1180–1078 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1040 a.E.V.</t>
+  </si>
+  <si>
+    <t>1077–c. 1040 a.E.V.</t>
+  </si>
+  <si>
+    <t>580 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1027–910 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 920–580 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 460 a.E.V.</t>
+  </si>
+  <si>
+    <t>Dopo 1 Cronache 9:44: 1077–1037 a.E.V.</t>
+  </si>
+  <si>
+    <t>1037–537 a.E.V.</t>
+  </si>
+  <si>
+    <t>537–c. 467 a.E.V.</t>
+  </si>
+  <si>
+    <t>dopo il 443 a.E.V.</t>
+  </si>
+  <si>
+    <t>456–dopo il 443 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 475 a.E.V.</t>
+  </si>
+  <si>
+    <t>493–c. 475 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1473 a.E.V.</t>
+  </si>
+  <si>
+    <t>Oltre 140 anni tra il 1657 e il 1473 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 717 a.E.V.</t>
+  </si>
+  <si>
+    <t>prima del 1000 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 1020 a.E.V.</t>
+  </si>
+  <si>
+    <t>dopo il 732 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 778–dopo il 732 a.E.V.</t>
+  </si>
+  <si>
+    <t>647–580 a.E.V.</t>
+  </si>
+  <si>
+    <t>607 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 591 a.E.V.</t>
+  </si>
+  <si>
+    <t>613–c. 591 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 536 a.E.V.</t>
+  </si>
+  <si>
+    <t>618–c. 536 a.E.V.</t>
+  </si>
+  <si>
+    <t>dopo il 745 a.E.V.</t>
+  </si>
+  <si>
+    <t>prima del 804–dopo il 745 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 820 a.E.V. (?)</t>
+  </si>
+  <si>
+    <t>c. 804 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 607 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 844 a.E.V.</t>
+  </si>
+  <si>
+    <t>prima del 717 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 777–717 a.E.V.</t>
+  </si>
+  <si>
+    <t>prima del 632 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 628 a.E.V. (?)</t>
+  </si>
+  <si>
+    <t>prima del 648 a.E.V.</t>
+  </si>
+  <si>
+    <t>520 a.E.V.</t>
+  </si>
+  <si>
+    <t>112 giorni (520 a.E.V.)</t>
+  </si>
+  <si>
+    <t>518 a.E.V.</t>
+  </si>
+  <si>
+    <t>520–518 a.E.V.</t>
+  </si>
+  <si>
+    <t>c. 41 E.V.</t>
+  </si>
+  <si>
+    <t>2 a.E.V.–33 E.V.</t>
+  </si>
+  <si>
+    <t>c. 60–65 E.V.</t>
+  </si>
+  <si>
+    <t>29–33 E.V.</t>
+  </si>
+  <si>
+    <t>c. 56–58 E.V.</t>
+  </si>
+  <si>
+    <t>3 a.E.V.–33 E.V.</t>
+  </si>
+  <si>
+    <t>c. 98 E.V.</t>
+  </si>
+  <si>
+    <t>Dopo il prologo, 29–33 E.V.</t>
+  </si>
+  <si>
+    <t>c. 61 E.V.</t>
+  </si>
+  <si>
+    <t>33–c. 61 E.V.</t>
+  </si>
+  <si>
+    <t>c. 56 E.V.</t>
+  </si>
+  <si>
+    <t>c. 55 E.V.</t>
+  </si>
+  <si>
+    <t>c. 50–52 E.V.</t>
+  </si>
+  <si>
+    <t>c. 60–61 E.V.</t>
+  </si>
+  <si>
+    <t>c. 50 E.V.</t>
+  </si>
+  <si>
+    <t>c. 51 E.V.</t>
+  </si>
+  <si>
+    <t>c. 61–64 E.V.</t>
+  </si>
+  <si>
+    <t>c. 65 E.V.</t>
+  </si>
+  <si>
+    <t>prima del 62 E.V.</t>
+  </si>
+  <si>
+    <t>c. 62–64 E.V.</t>
+  </si>
+  <si>
+    <t>c. 64 E.V.</t>
+  </si>
+  <si>
+    <t>c. 96 E.V.</t>
   </si>
 </sst>
 </file>
@@ -1047,15 +1047,15 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1064,15 +1064,15 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1081,253 +1081,253 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -1336,826 +1336,826 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="E45" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="D55" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E57" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="E59" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D60" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E61" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E62" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E63" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E64" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E65" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="B66" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" t="s">
         <v>186</v>
       </c>
-      <c r="C66" t="s">
-        <v>187</v>
-      </c>
-      <c r="D66" t="s">
-        <v>169</v>
-      </c>
       <c r="E66" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
         <v>190</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
